--- a/data/trans_orig/IQ2606_R2-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ2606_R2-Habitat-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>87952</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>78027</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>97354</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>59,42%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>52,72%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>65,78%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>103</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>76967</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>66435</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>86598</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>66433</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>87066</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>55,78%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>48,14%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>62,75%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>87952</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>77603</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>97430</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>59,42%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>52,43%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>65,83%</t>
+          <t>63,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>151338</t>
+          <t>149766</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>178150</t>
+          <t>178434</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>52,91%</t>
+          <t>52,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>62,29%</t>
+          <t>62,39%</t>
         </is>
       </c>
     </row>
@@ -840,69 +840,69 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>60056</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>50654</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>69981</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>40,58%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>34,22%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>47,28%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
           <t>61028</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>51397</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>71560</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>50929</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>71562</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>44,22%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>37,25%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>36,91%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>51,86%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>60056</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>50578</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>70405</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>40,58%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>34,17%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>47,57%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>168</t>
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>107854</t>
+          <t>107570</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>134666</t>
+          <t>136238</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>37,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>47,09%</t>
+          <t>47,63%</t>
         </is>
       </c>
     </row>
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>148008</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>148008</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>148008</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>137995</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>137995</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>137995</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>148008</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>148008</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>148008</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,72 +1065,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>118846</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>108184</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>132011</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>54,58%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>49,69%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>60,63%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>198</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>126677</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>114906</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>136769</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>115619</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>137682</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>63,77%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>57,85%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>68,85%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>172</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>118846</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>106904</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>131089</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>54,58%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>58,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>60,21%</t>
+          <t>69,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>228713</t>
+          <t>228825</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>261121</t>
+          <t>261363</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>54,93%</t>
+          <t>54,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>62,71%</t>
+          <t>62,77%</t>
         </is>
       </c>
     </row>
@@ -1178,72 +1178,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>98884</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>85719</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>109546</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>45,42%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>39,37%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>50,31%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>71963</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>61871</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>83734</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>60958</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>83021</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>36,23%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>31,15%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>42,15%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>98884</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>86641</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>110826</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>45,42%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>41,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>155249</t>
+          <t>155007</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>187657</t>
+          <t>187545</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>37,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>45,07%</t>
+          <t>45,04%</t>
         </is>
       </c>
     </row>
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>315</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>217730</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>217730</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>217730</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>307</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>198640</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>198640</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>198640</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>315</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>217730</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>217730</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>217730</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,72 +1408,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>100495</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>90978</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>110044</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>63,69%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>57,66%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>69,74%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>154</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>98642</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>89195</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>107131</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>88592</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>107881</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>65,56%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>59,28%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>71,2%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>100495</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>90314</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>110356</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>63,69%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>57,24%</t>
+          <t>58,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>69,94%</t>
+          <t>71,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>185587</t>
+          <t>185984</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>212439</t>
+          <t>212029</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>60,21%</t>
+          <t>60,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>68,92%</t>
+          <t>68,79%</t>
         </is>
       </c>
     </row>
@@ -1521,72 +1521,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>57287</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>47738</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>66804</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>36,31%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>30,26%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>42,34%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>51822</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>43333</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>61269</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>42583</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>61872</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>34,44%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>28,8%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>40,72%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>57287</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>47426</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>67468</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>36,31%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>42,76%</t>
+          <t>41,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>95806</t>
+          <t>96216</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>122658</t>
+          <t>122261</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>39,66%</t>
         </is>
       </c>
     </row>
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>157782</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>157782</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>157782</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>234</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>150464</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>150464</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>150464</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>157782</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>157782</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>157782</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,72 +1751,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>110360</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>97754</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>121455</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>54,65%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>48,41%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>60,14%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>168</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>126148</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>114681</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>138716</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>113958</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>137291</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>62,26%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>56,6%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>68,46%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>110360</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>97107</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>121499</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>54,65%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>48,09%</t>
+          <t>56,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>60,16%</t>
+          <t>67,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>220317</t>
+          <t>218458</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>253226</t>
+          <t>253498</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>54,46%</t>
+          <t>54,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>62,59%</t>
+          <t>62,66%</t>
         </is>
       </c>
     </row>
@@ -1864,72 +1864,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>91587</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>80492</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>104193</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>45,35%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>39,86%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>51,59%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>97</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>76464</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>63896</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>87931</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>65321</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>88654</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>37,74%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>31,54%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>43,4%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>91587</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>80448</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>104840</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>45,35%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>51,91%</t>
+          <t>43,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>151333</t>
+          <t>151061</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>184242</t>
+          <t>186101</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>45,54%</t>
+          <t>46,0%</t>
         </is>
       </c>
     </row>
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>274</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>201947</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>201947</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>201947</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>265</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>202612</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>202612</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>202612</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>274</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>201947</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>201947</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>201947</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2094,72 +2094,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>596</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>417652</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>392687</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>437154</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>57,57%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>54,13%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>60,26%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>623</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>428434</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>407089</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>448689</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>404431</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>447552</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>62,12%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>59,02%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>65,05%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>596</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>417652</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>395913</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>439847</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>57,57%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>54,57%</t>
+          <t>58,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>60,63%</t>
+          <t>64,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>816773</t>
+          <t>811897</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>879233</t>
+          <t>874003</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>57,72%</t>
+          <t>57,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>62,13%</t>
+          <t>61,76%</t>
         </is>
       </c>
     </row>
@@ -2207,72 +2207,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>438</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>307815</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>288313</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>332780</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>42,43%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>39,74%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>45,87%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>370</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>261277</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>241022</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>282622</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>242159</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>285280</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>37,88%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>34,95%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>40,98%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>438</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>307815</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>285620</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>329554</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>42,43%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>39,37%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>41,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>535945</t>
+          <t>541175</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>598405</t>
+          <t>603281</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>38,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>42,63%</t>
         </is>
       </c>
     </row>
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1034</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>725467</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>725467</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>725467</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>993</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>689711</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>689711</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>689711</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1034</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>725467</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>725467</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>725467</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2501,7 +2501,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2669,72 +2669,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>103787</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>93356</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>113313</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>70,45%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>63,37%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>76,92%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>130</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>92819</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>83118</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>101146</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>83021</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>100202</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>70,77%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>63,37%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>77,12%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>103787</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>94596</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>113476</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>70,45%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>64,21%</t>
+          <t>63,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,03%</t>
+          <t>76,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>183522</t>
+          <t>181918</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>210125</t>
+          <t>209386</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>65,9%</t>
+          <t>65,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>75,46%</t>
+          <t>75,19%</t>
         </is>
       </c>
     </row>
@@ -2782,72 +2782,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>43527</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>34001</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>53958</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>29,55%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>23,08%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>36,63%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>38342</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>30015</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>48043</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>30959</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>48140</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>29,23%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>22,88%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>36,63%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>43527</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>33838</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>52718</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>29,55%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>36,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>68349</t>
+          <t>69088</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>94952</t>
+          <t>96556</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>34,67%</t>
         </is>
       </c>
     </row>
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>147314</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>147314</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>147314</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>183</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>131161</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>131161</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>131161</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>147314</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>147314</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>147314</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3012,72 +3012,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>154343</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>143456</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>165978</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>69,8%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>64,88%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>75,06%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>238</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>146483</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>135119</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>156810</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>135912</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>155627</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>71,53%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>65,98%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>76,57%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>154343</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>142179</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>165046</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>69,8%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>64,3%</t>
+          <t>66,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>74,64%</t>
+          <t>75,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>285588</t>
+          <t>285419</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>315652</t>
+          <t>316160</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>67,05%</t>
+          <t>67,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>74,11%</t>
+          <t>74,23%</t>
         </is>
       </c>
     </row>
@@ -3125,72 +3125,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>66776</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>55141</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>77663</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>30,2%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>24,94%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>35,12%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>58306</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>47979</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>69670</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>49162</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>68877</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>28,47%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>23,43%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>34,02%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>66776</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>56073</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>78940</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>30,2%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>110256</t>
+          <t>109748</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>140320</t>
+          <t>140489</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>32,99%</t>
         </is>
       </c>
     </row>
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>327</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>221119</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>221119</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>221119</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>330</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>204789</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>204789</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>204789</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>327</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>221119</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>221119</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>221119</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3355,72 +3355,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>128818</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>119596</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>137271</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>77,83%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>72,26%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>82,94%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>200</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>120548</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>112659</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>128158</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>112016</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>127211</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>78,82%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>73,66%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>83,79%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>193</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>128818</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>119822</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>136895</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>77,83%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>72,4%</t>
+          <t>73,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>83,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>236560</t>
+          <t>236280</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>260708</t>
+          <t>260942</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>74,28%</t>
+          <t>74,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>81,94%</t>
         </is>
       </c>
     </row>
@@ -3473,67 +3473,67 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>36689</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>28236</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>45911</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>22,17%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>17,06%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>27,74%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
           <t>32396</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>24786</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>40285</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>25733</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>40928</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>21,18%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>16,21%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>26,34%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>36689</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>28612</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>45685</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>22,17%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>57743</t>
+          <t>57509</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>81891</t>
+          <t>82171</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,8%</t>
         </is>
       </c>
     </row>
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>165507</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>165507</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>165507</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>253</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>152944</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>152944</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>152944</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>246</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>165507</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>165507</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>165507</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3698,72 +3698,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>153647</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>143016</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>162644</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>75,79%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>70,55%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>80,23%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>200</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>146777</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>135553</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>157459</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>135143</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>157081</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>71,72%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>66,24%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>76,94%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>217</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>153647</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>143571</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>162341</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>75,79%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>70,82%</t>
+          <t>66,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>80,08%</t>
+          <t>76,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>285262</t>
+          <t>286596</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>316187</t>
+          <t>315633</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>70,03%</t>
+          <t>70,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>77,62%</t>
+          <t>77,48%</t>
         </is>
       </c>
     </row>
@@ -3811,72 +3811,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>49074</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>40077</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>59705</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>24,21%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>19,77%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>29,45%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>57869</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>47187</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>69093</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>47565</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>69503</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>28,28%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>23,06%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>33,76%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>49074</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>40380</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>59150</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>24,21%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>33,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>91180</t>
+          <t>91734</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>122105</t>
+          <t>120771</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>29,65%</t>
         </is>
       </c>
     </row>
@@ -3924,57 +3924,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>286</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>202721</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>202721</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>202721</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>277</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>204646</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>204646</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>204646</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>286</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>202721</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>202721</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>202721</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4041,72 +4041,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>778</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>540595</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>519925</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>560415</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>73,38%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>70,58%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>76,08%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>768</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>506627</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>487730</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>526672</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>485312</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>524695</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>73,05%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>70,32%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>75,94%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>778</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>540595</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>520202</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>559587</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>73,38%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>70,62%</t>
+          <t>69,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>75,96%</t>
+          <t>75,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1016482</t>
+          <t>1019468</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1072821</t>
+          <t>1074166</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>71,07%</t>
+          <t>71,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>75,01%</t>
+          <t>75,11%</t>
         </is>
       </c>
     </row>
@@ -4159,67 +4159,67 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>196066</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>176246</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>216736</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>26,62%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>23,92%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>29,42%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
           <t>186913</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>166868</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>205810</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>168845</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>208228</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>26,95%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>24,06%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>29,68%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>196066</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>177074</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>216459</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>26,62%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>357380</t>
+          <t>356035</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>413719</t>
+          <t>410733</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>28,72%</t>
         </is>
       </c>
     </row>
@@ -4267,57 +4267,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1053</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>736661</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>736661</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>736661</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1043</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>693540</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>693540</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>693540</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1053</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>736661</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>736661</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>736661</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4448,7 +4448,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4616,72 +4616,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>27425</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>23042</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>30103</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>84,46%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>70,96%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>92,71%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>23246</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>19814</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>25296</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>85,48%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>72,86%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>93,02%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>29864</t>
+          <t>23727</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25802</t>
+          <t>20428</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32736</t>
+          <t>25925</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>73,23%</t>
+          <t>73,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4691,32 +4691,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>53110</t>
+          <t>51152</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>47802</t>
+          <t>45636</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>56862</t>
+          <t>54831</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>84,96%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>76,57%</t>
+          <t>75,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>91,07%</t>
         </is>
       </c>
     </row>
@@ -4734,32 +4734,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3949</t>
+          <t>5047</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>2369</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7381</t>
+          <t>9430</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4769,32 +4769,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5369</t>
+          <t>4009</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2497</t>
+          <t>1811</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9431</t>
+          <t>7308</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4804,32 +4804,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>9318</t>
+          <t>9056</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5566</t>
+          <t>5377</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>14626</t>
+          <t>14572</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>24,2%</t>
         </is>
       </c>
     </row>
@@ -4842,57 +4842,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>32472</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>32472</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>32472</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>27195</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>27195</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>27195</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>35233</t>
+          <t>27736</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>35233</t>
+          <t>27736</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>35233</t>
+          <t>27736</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>62428</t>
+          <t>60208</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>62428</t>
+          <t>60208</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>62428</t>
+          <t>60208</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4959,72 +4959,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>51832</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>46943</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>55215</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>88,16%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>79,85%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>93,92%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>30689</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>25579</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>34680</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>78,06%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>65,06%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>88,21%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>55224</t>
+          <t>30784</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>49834</t>
+          <t>25119</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>58648</t>
+          <t>34585</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>78,2%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>79,71%</t>
+          <t>63,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>87,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5034,32 +5034,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>85913</t>
+          <t>82616</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>78637</t>
+          <t>75044</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>91889</t>
+          <t>88174</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>84,37%</t>
+          <t>84,17%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>77,22%</t>
+          <t>76,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>89,83%</t>
         </is>
       </c>
     </row>
@@ -5072,72 +5072,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>6960</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3577</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>11849</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>11,84%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>6,08%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>20,15%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>8625</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>4634</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>13735</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>21,94%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>11,79%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>34,94%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>7296</t>
+          <t>8580</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3872</t>
+          <t>4779</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>12686</t>
+          <t>14245</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5147,32 +5147,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>15921</t>
+          <t>15540</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>9945</t>
+          <t>9982</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>23197</t>
+          <t>23112</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>23,55%</t>
         </is>
       </c>
     </row>
@@ -5185,57 +5185,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>58792</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>58792</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>58792</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>39314</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>39314</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>39314</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>62520</t>
+          <t>39364</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>62520</t>
+          <t>39364</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>62520</t>
+          <t>39364</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5260,17 +5260,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>101834</t>
+          <t>98156</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>101834</t>
+          <t>98156</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>101834</t>
+          <t>98156</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5302,72 +5302,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>36951</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>32138</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>39485</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>89,02%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>77,43%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>95,13%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>26929</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>23369</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>29134</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>89,11%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>77,33%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>96,4%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>39008</t>
+          <t>23962</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>34130</t>
+          <t>19992</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>42057</t>
+          <t>25938</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>87,85%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>77,24%</t>
+          <t>73,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5377,32 +5377,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>65937</t>
+          <t>60913</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>60419</t>
+          <t>55500</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>69975</t>
+          <t>64396</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>88,56%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>81,2%</t>
+          <t>80,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>93,62%</t>
         </is>
       </c>
     </row>
@@ -5415,72 +5415,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>4556</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>9369</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>10,98%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>4,87%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>22,57%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>3292</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>1087</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>6852</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>10,89%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>3,6%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>22,67%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5180</t>
+          <t>3315</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2131</t>
+          <t>1339</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10058</t>
+          <t>7285</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5490,32 +5490,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>8472</t>
+          <t>7871</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4434</t>
+          <t>4388</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>13990</t>
+          <t>13284</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>19,31%</t>
         </is>
       </c>
     </row>
@@ -5528,57 +5528,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>41507</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>41507</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>41507</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>30221</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>30221</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>30221</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>44188</t>
+          <t>27277</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>44188</t>
+          <t>27277</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>44188</t>
+          <t>27277</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5603,17 +5603,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>74409</t>
+          <t>68784</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>74409</t>
+          <t>68784</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>74409</t>
+          <t>68784</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5645,72 +5645,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>36599</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>30169</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>40606</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>80,27%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>66,17%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>89,06%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>38364</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>33574</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>41957</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>83,87%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>73,4%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>91,73%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>40259</t>
+          <t>36468</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>34713</t>
+          <t>31453</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>44517</t>
+          <t>39535</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>80,79%</t>
+          <t>81,88%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>69,66%</t>
+          <t>70,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>78623</t>
+          <t>73067</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>70212</t>
+          <t>66282</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>84340</t>
+          <t>78745</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>81,07%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>73,47%</t>
+          <t>73,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>87,37%</t>
         </is>
       </c>
     </row>
@@ -5763,32 +5763,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>7377</t>
+          <t>8995</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3784</t>
+          <t>4988</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12167</t>
+          <t>15425</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>33,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5798,32 +5798,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>9570</t>
+          <t>8071</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5312</t>
+          <t>5004</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>15116</t>
+          <t>13086</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5833,32 +5833,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>16947</t>
+          <t>17066</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>11230</t>
+          <t>11388</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>25358</t>
+          <t>23851</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,46%</t>
         </is>
       </c>
     </row>
@@ -5871,57 +5871,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>45594</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>45594</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>45594</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>45741</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>45741</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>45741</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>49829</t>
+          <t>44539</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>49829</t>
+          <t>44539</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>49829</t>
+          <t>44539</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5946,17 +5946,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>95570</t>
+          <t>90133</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>95570</t>
+          <t>90133</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>95570</t>
+          <t>90133</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>152806</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>143923</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>160044</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>85,67%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>80,69%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>89,73%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>186</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>119227</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>111389</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>125669</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>83,69%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>78,18%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>88,21%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>216</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>164355</t>
+          <t>114941</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>154849</t>
+          <t>107006</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>172418</t>
+          <t>121901</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>82,74%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>80,75%</t>
+          <t>77,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>87,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>283582</t>
+          <t>267748</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>272672</t>
+          <t>255275</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>293736</t>
+          <t>278403</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>84,39%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>80,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>87,75%</t>
         </is>
       </c>
     </row>
@@ -6101,72 +6101,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>25559</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>18321</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>34442</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>14,33%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>10,27%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>19,31%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>23243</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>16801</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>31081</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>16,31%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>11,79%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>21,82%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>27415</t>
+          <t>23975</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19352</t>
+          <t>17015</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>36921</t>
+          <t>31910</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6176,32 +6176,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>50658</t>
+          <t>49533</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>40504</t>
+          <t>38878</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>61568</t>
+          <t>62006</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>19,54%</t>
         </is>
       </c>
     </row>
@@ -6214,57 +6214,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>178365</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>178365</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>178365</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>223</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>142470</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>142470</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>142470</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>191770</t>
+          <t>138916</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>191770</t>
+          <t>138916</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>191770</t>
+          <t>138916</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6289,17 +6289,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>334240</t>
+          <t>317281</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>334240</t>
+          <t>317281</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>334240</t>
+          <t>317281</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
